--- a/backend/data/financials_by_company/1721.HK.xlsx
+++ b/backend/data/financials_by_company/1721.HK.xlsx
@@ -657,59 +657,59 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C2" t="n">
         <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-466000</v>
+        <v>-203000</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G2" t="n">
-        <v>-3407000</v>
+        <v>-3140000</v>
       </c>
       <c r="H2" t="n">
-        <v>1595000</v>
+        <v>2278000</v>
       </c>
       <c r="I2" t="n">
-        <v>8904000</v>
+        <v>11098000</v>
       </c>
       <c r="J2" t="n">
-        <v>-466000</v>
+        <v>-202000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2061000</v>
+        <v>-2480000</v>
       </c>
       <c r="L2" t="n">
-        <v>93000</v>
+        <v>-61000</v>
       </c>
       <c r="M2" t="n">
-        <v>846000</v>
+        <v>60000</v>
       </c>
       <c r="N2" t="n">
-        <v>958000</v>
+        <v>20000</v>
       </c>
       <c r="O2" t="n">
-        <v>-3407000</v>
+        <v>-3140835</v>
       </c>
       <c r="P2" t="n">
-        <v>-3407000</v>
+        <v>-3140000</v>
       </c>
       <c r="Q2" t="n">
-        <v>19314000</v>
+        <v>18912000</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-3000000</v>
+        <v>-2479000</v>
       </c>
       <c r="T2" t="n">
         <v>1000000000</v>
@@ -718,139 +718,141 @@
         <v>1000000000</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0034</v>
+        <v>-0.0031</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0034</v>
+        <v>-0.0031</v>
       </c>
       <c r="X2" t="n">
-        <v>-3407000</v>
+        <v>-3140000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3407000</v>
+        <v>-3140000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-3407000</v>
+        <v>-3140000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3407000</v>
+        <v>-3140000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3407000</v>
+        <v>-3140000</v>
       </c>
       <c r="AD2" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2907000</v>
+        <v>-2540000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>93000</v>
+        <v>-61000</v>
       </c>
       <c r="AI2" t="n">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>846000</v>
+        <v>60000</v>
       </c>
       <c r="AK2" t="n">
-        <v>958000</v>
+        <v>20000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4438000</v>
+        <v>-2836000</v>
       </c>
       <c r="AM2" t="n">
-        <v>10410000</v>
+        <v>7814000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3223000</v>
+        <v>1690000</v>
       </c>
       <c r="AO2" t="n">
-        <v>7214000</v>
+        <v>6178000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2081000</v>
+        <v>547000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5133000</v>
+        <v>5631000</v>
       </c>
       <c r="AR2" t="n">
-        <v>5972000</v>
+        <v>4978000</v>
       </c>
       <c r="AS2" t="n">
-        <v>8904000</v>
+        <v>11098000</v>
       </c>
       <c r="AT2" t="n">
-        <v>14876000</v>
+        <v>16076000</v>
       </c>
       <c r="AU2" t="n">
-        <v>14876000</v>
+        <v>16076000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>165</v>
+        <v>26546.981954</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0.358743</v>
       </c>
       <c r="D3" t="n">
-        <v>-1546000</v>
+        <v>5147000</v>
       </c>
       <c r="E3" t="n">
-        <v>1000</v>
+        <v>74000</v>
       </c>
       <c r="F3" t="n">
-        <v>1000</v>
+        <v>74000</v>
       </c>
       <c r="G3" t="n">
-        <v>-4876000</v>
+        <v>2061000</v>
       </c>
       <c r="H3" t="n">
-        <v>1889000</v>
+        <v>1964000</v>
       </c>
       <c r="I3" t="n">
-        <v>10131000</v>
+        <v>12591000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1545000</v>
+        <v>5221000</v>
       </c>
       <c r="K3" t="n">
-        <v>-3434000</v>
+        <v>3257000</v>
       </c>
       <c r="L3" t="n">
-        <v>-58000</v>
+        <v>109000</v>
       </c>
       <c r="M3" t="n">
-        <v>693000</v>
+        <v>43000</v>
       </c>
       <c r="N3" t="n">
-        <v>659000</v>
+        <v>162000</v>
       </c>
       <c r="O3" t="n">
-        <v>-4876835</v>
+        <v>2013546.981954</v>
       </c>
       <c r="P3" t="n">
-        <v>-4876000</v>
+        <v>2061000</v>
       </c>
       <c r="Q3" t="n">
-        <v>19196000</v>
+        <v>20053000</v>
       </c>
       <c r="R3" t="n">
-        <v>71000</v>
+        <v>36000</v>
       </c>
       <c r="S3" t="n">
-        <v>-4069000</v>
+        <v>3105000</v>
       </c>
       <c r="T3" t="n">
         <v>1000000000</v>
@@ -859,141 +861,141 @@
         <v>1000000000</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0049</v>
+        <v>0.0021</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0049</v>
+        <v>0.0021</v>
       </c>
       <c r="X3" t="n">
-        <v>-4876000</v>
+        <v>2061000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-4876000</v>
+        <v>2061000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-4876000</v>
+        <v>2061000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4876000</v>
+        <v>2061000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4876000</v>
+        <v>2061000</v>
       </c>
       <c r="AD3" t="n">
-        <v>749000</v>
+        <v>1153000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-4127000</v>
+        <v>3214000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>74000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1000</v>
+        <v>-74000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-58000</v>
+        <v>109000</v>
       </c>
       <c r="AI3" t="n">
-        <v>24000</v>
+        <v>10000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>693000</v>
+        <v>43000</v>
       </c>
       <c r="AK3" t="n">
-        <v>659000</v>
+        <v>162000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3125000</v>
+        <v>3248000</v>
       </c>
       <c r="AM3" t="n">
-        <v>9065000</v>
+        <v>7462000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2816000</v>
+        <v>2094000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6268000</v>
+        <v>5411000</v>
       </c>
       <c r="AP3" t="n">
-        <v>758000</v>
+        <v>220000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5510000</v>
+        <v>5191000</v>
       </c>
       <c r="AR3" t="n">
-        <v>5940000</v>
+        <v>10710000</v>
       </c>
       <c r="AS3" t="n">
-        <v>10131000</v>
+        <v>12591000</v>
       </c>
       <c r="AT3" t="n">
-        <v>16071000</v>
+        <v>23301000</v>
       </c>
       <c r="AU3" t="n">
-        <v>16071000</v>
+        <v>23301000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>26546.981954</v>
+        <v>165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.358743</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>5147000</v>
+        <v>-1546000</v>
       </c>
       <c r="E4" t="n">
-        <v>74000</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="n">
-        <v>74000</v>
+        <v>1000</v>
       </c>
       <c r="G4" t="n">
-        <v>2061000</v>
+        <v>-4876000</v>
       </c>
       <c r="H4" t="n">
-        <v>1964000</v>
+        <v>1889000</v>
       </c>
       <c r="I4" t="n">
-        <v>12591000</v>
+        <v>10131000</v>
       </c>
       <c r="J4" t="n">
-        <v>5221000</v>
+        <v>-1545000</v>
       </c>
       <c r="K4" t="n">
-        <v>3257000</v>
+        <v>-3434000</v>
       </c>
       <c r="L4" t="n">
-        <v>109000</v>
+        <v>-58000</v>
       </c>
       <c r="M4" t="n">
-        <v>43000</v>
+        <v>693000</v>
       </c>
       <c r="N4" t="n">
-        <v>162000</v>
+        <v>659000</v>
       </c>
       <c r="O4" t="n">
-        <v>2013546.981954</v>
+        <v>-4876835</v>
       </c>
       <c r="P4" t="n">
-        <v>2061000</v>
+        <v>-4876000</v>
       </c>
       <c r="Q4" t="n">
-        <v>20053000</v>
+        <v>19196000</v>
       </c>
       <c r="R4" t="n">
-        <v>36000</v>
+        <v>71000</v>
       </c>
       <c r="S4" t="n">
-        <v>3105000</v>
+        <v>-4069000</v>
       </c>
       <c r="T4" t="n">
         <v>1000000000</v>
@@ -1002,139 +1004,139 @@
         <v>1000000000</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0021</v>
+        <v>-0.0049</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0021</v>
+        <v>-0.0049</v>
       </c>
       <c r="X4" t="n">
-        <v>2061000</v>
+        <v>-4876000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2061000</v>
+        <v>-4876000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2061000</v>
+        <v>-4876000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2061000</v>
+        <v>-4876000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2061000</v>
+        <v>-4876000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1153000</v>
+        <v>749000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3214000</v>
+        <v>-4127000</v>
       </c>
       <c r="AF4" t="n">
-        <v>74000</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-74000</v>
+        <v>-1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>109000</v>
+        <v>-58000</v>
       </c>
       <c r="AI4" t="n">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>43000</v>
+        <v>693000</v>
       </c>
       <c r="AK4" t="n">
-        <v>162000</v>
+        <v>659000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3248000</v>
+        <v>-3125000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7462000</v>
+        <v>9065000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2094000</v>
+        <v>2816000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5411000</v>
+        <v>6268000</v>
       </c>
       <c r="AP4" t="n">
-        <v>220000</v>
+        <v>758000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5191000</v>
+        <v>5510000</v>
       </c>
       <c r="AR4" t="n">
-        <v>10710000</v>
+        <v>5940000</v>
       </c>
       <c r="AS4" t="n">
-        <v>12591000</v>
+        <v>10131000</v>
       </c>
       <c r="AT4" t="n">
-        <v>23301000</v>
+        <v>16071000</v>
       </c>
       <c r="AU4" t="n">
-        <v>23301000</v>
+        <v>16071000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>-203000</v>
+        <v>-466000</v>
       </c>
       <c r="E5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-3140000</v>
+        <v>-3407000</v>
       </c>
       <c r="H5" t="n">
-        <v>2278000</v>
+        <v>1595000</v>
       </c>
       <c r="I5" t="n">
-        <v>11098000</v>
+        <v>8904000</v>
       </c>
       <c r="J5" t="n">
-        <v>-202000</v>
+        <v>-466000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2480000</v>
+        <v>-2061000</v>
       </c>
       <c r="L5" t="n">
-        <v>-61000</v>
+        <v>93000</v>
       </c>
       <c r="M5" t="n">
-        <v>60000</v>
+        <v>846000</v>
       </c>
       <c r="N5" t="n">
-        <v>20000</v>
+        <v>958000</v>
       </c>
       <c r="O5" t="n">
-        <v>-3140835</v>
+        <v>-3407000</v>
       </c>
       <c r="P5" t="n">
-        <v>-3140000</v>
+        <v>-3407000</v>
       </c>
       <c r="Q5" t="n">
-        <v>18912000</v>
+        <v>19314000</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-2479000</v>
+        <v>-3000000</v>
       </c>
       <c r="T5" t="n">
         <v>1000000000</v>
@@ -1143,82 +1145,80 @@
         <v>1000000000</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0034</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0034</v>
       </c>
       <c r="X5" t="n">
-        <v>-3140000</v>
+        <v>-3407000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3140000</v>
+        <v>-3407000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3140000</v>
+        <v>-3407000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3140000</v>
+        <v>-3407000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3140000</v>
+        <v>-3407000</v>
       </c>
       <c r="AD5" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2540000</v>
+        <v>-2907000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-1000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-61000</v>
+        <v>93000</v>
       </c>
       <c r="AI5" t="n">
-        <v>21000</v>
+        <v>19000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>60000</v>
+        <v>846000</v>
       </c>
       <c r="AK5" t="n">
-        <v>20000</v>
+        <v>958000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-2836000</v>
+        <v>-4438000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7814000</v>
+        <v>10410000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1690000</v>
+        <v>3223000</v>
       </c>
       <c r="AO5" t="n">
-        <v>6178000</v>
+        <v>7214000</v>
       </c>
       <c r="AP5" t="n">
-        <v>547000</v>
+        <v>2081000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5631000</v>
+        <v>5133000</v>
       </c>
       <c r="AR5" t="n">
-        <v>4978000</v>
+        <v>5972000</v>
       </c>
       <c r="AS5" t="n">
-        <v>11098000</v>
+        <v>8904000</v>
       </c>
       <c r="AT5" t="n">
-        <v>16076000</v>
+        <v>14876000</v>
       </c>
       <c r="AU5" t="n">
-        <v>16076000</v>
+        <v>14876000</v>
       </c>
     </row>
   </sheetData>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1000000000</v>
@@ -1548,37 +1548,37 @@
         <v>1000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>15574000</v>
+        <v>1355000</v>
       </c>
       <c r="E2" t="n">
-        <v>30155000</v>
+        <v>32643000</v>
       </c>
       <c r="F2" t="n">
-        <v>45036000</v>
+        <v>32901000</v>
       </c>
       <c r="G2" t="n">
-        <v>35565000</v>
+        <v>20912000</v>
       </c>
       <c r="H2" t="n">
-        <v>30155000</v>
+        <v>32643000</v>
       </c>
       <c r="I2" t="n">
-        <v>699000</v>
+        <v>1134000</v>
       </c>
       <c r="J2" t="n">
-        <v>30161000</v>
+        <v>32680000</v>
       </c>
       <c r="K2" t="n">
-        <v>44883000</v>
+        <v>32680000</v>
       </c>
       <c r="L2" t="n">
-        <v>30161000</v>
+        <v>32680000</v>
       </c>
       <c r="M2" t="n">
-        <v>30161000</v>
+        <v>32680000</v>
       </c>
       <c r="N2" t="n">
-        <v>3624000</v>
+        <v>9911000</v>
       </c>
       <c r="O2" t="n">
         <v>18605000</v>
@@ -1590,137 +1590,139 @@
         <v>1695000</v>
       </c>
       <c r="R2" t="n">
-        <v>21733000</v>
+        <v>7516000</v>
       </c>
       <c r="S2" t="n">
-        <v>16004000</v>
+        <v>1934000</v>
       </c>
       <c r="T2" t="n">
-        <v>810000</v>
+        <v>1191000</v>
       </c>
       <c r="U2" t="n">
-        <v>15094000</v>
+        <v>657000</v>
       </c>
       <c r="V2" t="n">
-        <v>372000</v>
+        <v>657000</v>
       </c>
       <c r="W2" t="n">
-        <v>14722000</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>100000</v>
+        <v>86000</v>
       </c>
       <c r="Y2" t="n">
-        <v>5729000</v>
+        <v>5582000</v>
       </c>
       <c r="Z2" t="n">
-        <v>480000</v>
+        <v>698000</v>
       </c>
       <c r="AA2" t="n">
-        <v>327000</v>
+        <v>477000</v>
       </c>
       <c r="AB2" t="n">
-        <v>153000</v>
+        <v>221000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2204000</v>
+        <v>2358000</v>
       </c>
       <c r="AD2" t="n">
-        <v>351000</v>
+        <v>231000</v>
       </c>
       <c r="AE2" t="n">
-        <v>940000</v>
+        <v>557000</v>
       </c>
       <c r="AF2" t="n">
-        <v>913000</v>
+        <v>1570000</v>
       </c>
       <c r="AG2" t="n">
-        <v>51894000</v>
+        <v>40196000</v>
       </c>
       <c r="AH2" t="n">
-        <v>10600000</v>
+        <v>13702000</v>
       </c>
       <c r="AI2" t="n">
-        <v>14000</v>
+        <v>81000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6000</v>
+        <v>37000</v>
       </c>
       <c r="AK2" t="n">
-        <v>6000</v>
+        <v>37000</v>
       </c>
       <c r="AL2" t="n">
-        <v>10580000</v>
+        <v>13584000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-21312000</v>
+        <v>-19212000</v>
       </c>
       <c r="AN2" t="n">
-        <v>31892000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>32796000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>13584000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>18143000</v>
+        <v>18607000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13749000</v>
+        <v>14189000</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>41294000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>26494000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>54000</v>
+      </c>
       <c r="AU2" t="n">
-        <v>346000</v>
+        <v>253000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1896000</v>
+        <v>1561000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-600000</v>
+        <v>-139000</v>
       </c>
       <c r="AX2" t="n">
-        <v>510000</v>
+        <v>477000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1048000</v>
+        <v>95000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>938000</v>
+        <v>1128000</v>
       </c>
       <c r="BA2" t="n">
-        <v>291000</v>
+        <v>13000</v>
       </c>
       <c r="BB2" t="n">
-        <v>2482000</v>
+        <v>3893000</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>2482000</v>
+        <v>3627000</v>
       </c>
       <c r="BE2" t="n">
-        <v>36279000</v>
+        <v>20986000</v>
       </c>
       <c r="BF2" t="n">
-        <v>54000</v>
+        <v>7054000</v>
       </c>
       <c r="BG2" t="n">
-        <v>36225000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>25608000</v>
-      </c>
+        <v>13932000</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
-        <v>10617000</v>
+        <v>13932000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1000000000</v>
@@ -1729,37 +1731,37 @@
         <v>1000000000</v>
       </c>
       <c r="D3" t="n">
-        <v>14464000</v>
+        <v>1038000</v>
       </c>
       <c r="E3" t="n">
-        <v>34097000</v>
+        <v>34495000</v>
       </c>
       <c r="F3" t="n">
-        <v>47807000</v>
+        <v>34886000</v>
       </c>
       <c r="G3" t="n">
-        <v>37680000</v>
+        <v>23780000</v>
       </c>
       <c r="H3" t="n">
-        <v>34097000</v>
+        <v>34495000</v>
       </c>
       <c r="I3" t="n">
-        <v>769000</v>
+        <v>674000</v>
       </c>
       <c r="J3" t="n">
-        <v>34112000</v>
+        <v>34522000</v>
       </c>
       <c r="K3" t="n">
-        <v>47660000</v>
+        <v>34794000</v>
       </c>
       <c r="L3" t="n">
-        <v>34112000</v>
+        <v>34522000</v>
       </c>
       <c r="M3" t="n">
-        <v>34112000</v>
+        <v>34522000</v>
       </c>
       <c r="N3" t="n">
-        <v>7050000</v>
+        <v>11972000</v>
       </c>
       <c r="O3" t="n">
         <v>18605000</v>
@@ -1771,139 +1773,141 @@
         <v>1695000</v>
       </c>
       <c r="R3" t="n">
-        <v>21073000</v>
+        <v>9333000</v>
       </c>
       <c r="S3" t="n">
-        <v>14969000</v>
+        <v>1923000</v>
       </c>
       <c r="T3" t="n">
-        <v>931000</v>
+        <v>1112000</v>
       </c>
       <c r="U3" t="n">
-        <v>13943000</v>
+        <v>720000</v>
       </c>
       <c r="V3" t="n">
-        <v>395000</v>
+        <v>448000</v>
       </c>
       <c r="W3" t="n">
-        <v>13548000</v>
+        <v>272000</v>
       </c>
       <c r="X3" t="n">
-        <v>95000</v>
+        <v>91000</v>
       </c>
       <c r="Y3" t="n">
-        <v>6104000</v>
+        <v>7410000</v>
       </c>
       <c r="Z3" t="n">
-        <v>521000</v>
+        <v>318000</v>
       </c>
       <c r="AA3" t="n">
-        <v>374000</v>
+        <v>226000</v>
       </c>
       <c r="AB3" t="n">
-        <v>147000</v>
+        <v>92000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1632000</v>
+        <v>3635000</v>
       </c>
       <c r="AD3" t="n">
-        <v>232000</v>
+        <v>693000</v>
       </c>
       <c r="AE3" t="n">
-        <v>819000</v>
+        <v>1164000</v>
       </c>
       <c r="AF3" t="n">
-        <v>581000</v>
+        <v>1778000</v>
       </c>
       <c r="AG3" t="n">
-        <v>55185000</v>
+        <v>43855000</v>
       </c>
       <c r="AH3" t="n">
-        <v>11401000</v>
+        <v>12665000</v>
       </c>
       <c r="AI3" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="AK3" t="n">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="AL3" t="n">
-        <v>11314000</v>
+        <v>12638000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-19997000</v>
+        <v>-18708000</v>
       </c>
       <c r="AN3" t="n">
-        <v>31311000</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>31346000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>12638000</v>
+      </c>
       <c r="AP3" t="n">
-        <v>17705000</v>
+        <v>17746000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13606000</v>
+        <v>13600000</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>43784000</v>
+        <v>31190000</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="AU3" t="n">
-        <v>373000</v>
+        <v>298000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1756000</v>
+        <v>3251000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-663000</v>
+        <v>-163000</v>
       </c>
       <c r="AX3" t="n">
-        <v>624000</v>
+        <v>472000</v>
       </c>
       <c r="AY3" t="n">
-        <v>629000</v>
+        <v>868000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1166000</v>
+        <v>2074000</v>
       </c>
       <c r="BA3" t="n">
-        <v>112000</v>
+        <v>110000</v>
       </c>
       <c r="BB3" t="n">
-        <v>2558000</v>
+        <v>3999000</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>2558000</v>
+        <v>3999000</v>
       </c>
       <c r="BE3" t="n">
-        <v>38985000</v>
+        <v>23480000</v>
       </c>
       <c r="BF3" t="n">
-        <v>49000</v>
+        <v>10903000</v>
       </c>
       <c r="BG3" t="n">
-        <v>38936000</v>
+        <v>12577000</v>
       </c>
       <c r="BH3" t="n">
-        <v>19004000</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>19932000</v>
+        <v>12577000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1000000000</v>
@@ -1912,37 +1916,37 @@
         <v>1000000000</v>
       </c>
       <c r="D4" t="n">
-        <v>1038000</v>
+        <v>14464000</v>
       </c>
       <c r="E4" t="n">
-        <v>34495000</v>
+        <v>34097000</v>
       </c>
       <c r="F4" t="n">
-        <v>34886000</v>
+        <v>47807000</v>
       </c>
       <c r="G4" t="n">
-        <v>23780000</v>
+        <v>37680000</v>
       </c>
       <c r="H4" t="n">
-        <v>34495000</v>
+        <v>34097000</v>
       </c>
       <c r="I4" t="n">
-        <v>674000</v>
+        <v>769000</v>
       </c>
       <c r="J4" t="n">
-        <v>34522000</v>
+        <v>34112000</v>
       </c>
       <c r="K4" t="n">
-        <v>34794000</v>
+        <v>47660000</v>
       </c>
       <c r="L4" t="n">
-        <v>34522000</v>
+        <v>34112000</v>
       </c>
       <c r="M4" t="n">
-        <v>34522000</v>
+        <v>34112000</v>
       </c>
       <c r="N4" t="n">
-        <v>11972000</v>
+        <v>7050000</v>
       </c>
       <c r="O4" t="n">
         <v>18605000</v>
@@ -1954,141 +1958,139 @@
         <v>1695000</v>
       </c>
       <c r="R4" t="n">
-        <v>9333000</v>
+        <v>21073000</v>
       </c>
       <c r="S4" t="n">
-        <v>1923000</v>
+        <v>14969000</v>
       </c>
       <c r="T4" t="n">
-        <v>1112000</v>
+        <v>931000</v>
       </c>
       <c r="U4" t="n">
-        <v>720000</v>
+        <v>13943000</v>
       </c>
       <c r="V4" t="n">
-        <v>448000</v>
+        <v>395000</v>
       </c>
       <c r="W4" t="n">
-        <v>272000</v>
+        <v>13548000</v>
       </c>
       <c r="X4" t="n">
-        <v>91000</v>
+        <v>95000</v>
       </c>
       <c r="Y4" t="n">
-        <v>7410000</v>
+        <v>6104000</v>
       </c>
       <c r="Z4" t="n">
-        <v>318000</v>
+        <v>521000</v>
       </c>
       <c r="AA4" t="n">
-        <v>226000</v>
+        <v>374000</v>
       </c>
       <c r="AB4" t="n">
-        <v>92000</v>
+        <v>147000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3635000</v>
+        <v>1632000</v>
       </c>
       <c r="AD4" t="n">
-        <v>693000</v>
+        <v>232000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1164000</v>
+        <v>819000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1778000</v>
+        <v>581000</v>
       </c>
       <c r="AG4" t="n">
-        <v>43855000</v>
+        <v>55185000</v>
       </c>
       <c r="AH4" t="n">
-        <v>12665000</v>
+        <v>11401000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="AK4" t="n">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="AL4" t="n">
-        <v>12638000</v>
+        <v>11314000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-18708000</v>
+        <v>-19997000</v>
       </c>
       <c r="AN4" t="n">
-        <v>31346000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>12638000</v>
-      </c>
+        <v>31311000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>17746000</v>
+        <v>17705000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13600000</v>
+        <v>13606000</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>31190000</v>
+        <v>43784000</v>
       </c>
       <c r="AT4" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>298000</v>
+        <v>373000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3251000</v>
+        <v>1756000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-163000</v>
+        <v>-663000</v>
       </c>
       <c r="AX4" t="n">
-        <v>472000</v>
+        <v>624000</v>
       </c>
       <c r="AY4" t="n">
-        <v>868000</v>
+        <v>629000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2074000</v>
+        <v>1166000</v>
       </c>
       <c r="BA4" t="n">
-        <v>110000</v>
+        <v>112000</v>
       </c>
       <c r="BB4" t="n">
-        <v>3999000</v>
+        <v>2558000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3999000</v>
+        <v>2558000</v>
       </c>
       <c r="BE4" t="n">
-        <v>23480000</v>
+        <v>38985000</v>
       </c>
       <c r="BF4" t="n">
-        <v>10903000</v>
+        <v>49000</v>
       </c>
       <c r="BG4" t="n">
-        <v>12577000</v>
+        <v>38936000</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>19004000</v>
       </c>
       <c r="BI4" t="n">
-        <v>12577000</v>
+        <v>19932000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1000000000</v>
@@ -2097,37 +2099,37 @@
         <v>1000000000</v>
       </c>
       <c r="D5" t="n">
-        <v>1355000</v>
+        <v>15574000</v>
       </c>
       <c r="E5" t="n">
-        <v>32643000</v>
+        <v>30155000</v>
       </c>
       <c r="F5" t="n">
-        <v>32901000</v>
+        <v>45036000</v>
       </c>
       <c r="G5" t="n">
-        <v>20912000</v>
+        <v>35565000</v>
       </c>
       <c r="H5" t="n">
-        <v>32643000</v>
+        <v>30155000</v>
       </c>
       <c r="I5" t="n">
-        <v>1134000</v>
+        <v>699000</v>
       </c>
       <c r="J5" t="n">
-        <v>32680000</v>
+        <v>30161000</v>
       </c>
       <c r="K5" t="n">
-        <v>32680000</v>
+        <v>44883000</v>
       </c>
       <c r="L5" t="n">
-        <v>32680000</v>
+        <v>30161000</v>
       </c>
       <c r="M5" t="n">
-        <v>32680000</v>
+        <v>30161000</v>
       </c>
       <c r="N5" t="n">
-        <v>9911000</v>
+        <v>3624000</v>
       </c>
       <c r="O5" t="n">
         <v>18605000</v>
@@ -2139,134 +2141,132 @@
         <v>1695000</v>
       </c>
       <c r="R5" t="n">
-        <v>7516000</v>
+        <v>21733000</v>
       </c>
       <c r="S5" t="n">
-        <v>1934000</v>
+        <v>16004000</v>
       </c>
       <c r="T5" t="n">
-        <v>1191000</v>
+        <v>810000</v>
       </c>
       <c r="U5" t="n">
-        <v>657000</v>
+        <v>15094000</v>
       </c>
       <c r="V5" t="n">
-        <v>657000</v>
+        <v>372000</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>14722000</v>
       </c>
       <c r="X5" t="n">
-        <v>86000</v>
+        <v>100000</v>
       </c>
       <c r="Y5" t="n">
-        <v>5582000</v>
+        <v>5729000</v>
       </c>
       <c r="Z5" t="n">
-        <v>698000</v>
+        <v>480000</v>
       </c>
       <c r="AA5" t="n">
-        <v>477000</v>
+        <v>327000</v>
       </c>
       <c r="AB5" t="n">
-        <v>221000</v>
+        <v>153000</v>
       </c>
       <c r="AC5" t="n">
-        <v>2358000</v>
+        <v>2204000</v>
       </c>
       <c r="AD5" t="n">
-        <v>231000</v>
+        <v>351000</v>
       </c>
       <c r="AE5" t="n">
-        <v>557000</v>
+        <v>940000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1570000</v>
+        <v>913000</v>
       </c>
       <c r="AG5" t="n">
-        <v>40196000</v>
+        <v>51894000</v>
       </c>
       <c r="AH5" t="n">
-        <v>13702000</v>
+        <v>10600000</v>
       </c>
       <c r="AI5" t="n">
-        <v>81000</v>
+        <v>14000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>37000</v>
+        <v>6000</v>
       </c>
       <c r="AK5" t="n">
-        <v>37000</v>
+        <v>6000</v>
       </c>
       <c r="AL5" t="n">
-        <v>13584000</v>
+        <v>10580000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-19212000</v>
+        <v>-21312000</v>
       </c>
       <c r="AN5" t="n">
-        <v>32796000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>13584000</v>
-      </c>
+        <v>31892000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>18607000</v>
+        <v>18143000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14189000</v>
+        <v>13749000</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>26494000</v>
-      </c>
-      <c r="AT5" t="n">
+        <v>41294000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>346000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1896000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>510000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1048000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>938000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>291000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2482000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2482000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>36279000</v>
+      </c>
+      <c r="BF5" t="n">
         <v>54000</v>
       </c>
-      <c r="AU5" t="n">
-        <v>253000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1561000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-139000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>477000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>95000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1128000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3893000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3627000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>20986000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7054000</v>
-      </c>
       <c r="BG5" t="n">
-        <v>13932000</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
+        <v>36225000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>25608000</v>
+      </c>
       <c r="BI5" t="n">
-        <v>13932000</v>
+        <v>10617000</v>
       </c>
     </row>
   </sheetData>
@@ -2482,466 +2482,466 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-3049000</v>
+        <v>-1579000</v>
       </c>
       <c r="C2" t="n">
-        <v>-147000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
+        <v>-693000</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-281000</v>
+        <v>-499000</v>
       </c>
       <c r="F2" t="n">
-        <v>36225000</v>
+        <v>13932000</v>
       </c>
       <c r="G2" t="n">
-        <v>38936000</v>
+        <v>10602000</v>
       </c>
       <c r="H2" t="n">
-        <v>59000</v>
+        <v>191000</v>
       </c>
       <c r="I2" t="n">
-        <v>-2770000</v>
+        <v>3139000</v>
       </c>
       <c r="J2" t="n">
-        <v>-674000</v>
+        <v>-1138000</v>
       </c>
       <c r="K2" t="n">
-        <v>-56000</v>
+        <v>-78000</v>
       </c>
       <c r="L2" t="n">
-        <v>-147000</v>
+        <v>-693000</v>
       </c>
       <c r="M2" t="n">
-        <v>-147000</v>
+        <v>-693000</v>
       </c>
       <c r="N2" t="n">
-        <v>-147000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
+        <v>-693000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>672000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>5357000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5828000</v>
+      </c>
       <c r="R2" t="n">
-        <v>958000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-12000</v>
+      </c>
       <c r="W2" t="n">
-        <v>-281000</v>
+        <v>-479000</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-281000</v>
+        <v>-487000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2768000</v>
+        <v>-1080000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-514000</v>
+        <v>-191000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-601000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>60000</v>
-      </c>
+        <v>-545000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>-616000</v>
+        <v>1649000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-37000</v>
+        <v>-577000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-8000</v>
+        <v>-1617000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-93000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>61000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-142000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>1595000</v>
+        <v>2278000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1586000</v>
+        <v>2257000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-185000</v>
+        <v>-75000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2907000</v>
+        <v>-2540000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1511000</v>
+        <v>3047000</v>
       </c>
       <c r="C3" t="n">
-        <v>-142000</v>
+        <v>-244000</v>
       </c>
       <c r="D3" t="n">
-        <v>16770000</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-13000</v>
+        <v>-817000</v>
       </c>
       <c r="F3" t="n">
-        <v>38936000</v>
+        <v>12577000</v>
       </c>
       <c r="G3" t="n">
-        <v>12577000</v>
+        <v>13932000</v>
       </c>
       <c r="H3" t="n">
-        <v>-47000</v>
+        <v>-23000</v>
       </c>
       <c r="I3" t="n">
-        <v>26406000</v>
+        <v>-1332000</v>
       </c>
       <c r="J3" t="n">
-        <v>16150000</v>
+        <v>-770000</v>
       </c>
       <c r="K3" t="n">
-        <v>-60000</v>
+        <v>-48000</v>
       </c>
       <c r="L3" t="n">
-        <v>16628000</v>
+        <v>-244000</v>
       </c>
       <c r="M3" t="n">
-        <v>16628000</v>
+        <v>-244000</v>
       </c>
       <c r="N3" t="n">
-        <v>-142000</v>
+        <v>-244000</v>
       </c>
       <c r="O3" t="n">
-        <v>16770000</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>11754000</v>
+        <v>-4426000</v>
       </c>
       <c r="Q3" t="n">
-        <v>11107000</v>
+        <v>-3847000</v>
       </c>
       <c r="R3" t="n">
-        <v>659000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+        <v>162000</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="W3" t="n">
-        <v>-12000</v>
+        <v>-736000</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>76000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-13000</v>
+        <v>-812000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1498000</v>
+        <v>3864000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1262000</v>
+        <v>-609000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1132000</v>
+        <v>-546000</v>
       </c>
       <c r="AC3" t="n">
-        <v>308000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1353000</v>
+        <v>1601000</v>
       </c>
       <c r="AE3" t="n">
-        <v>921000</v>
+        <v>-1714000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1256000</v>
+        <v>-433000</v>
       </c>
       <c r="AG3" t="n">
-        <v>58000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>-109000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>24000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>1889000</v>
+        <v>1964000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1877000</v>
+        <v>1949000</v>
       </c>
       <c r="AL3" t="n">
-        <v>313000</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1000</v>
+        <v>-74000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-4127000</v>
+        <v>3214000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3047000</v>
+        <v>-1511000</v>
       </c>
       <c r="C4" t="n">
-        <v>-244000</v>
+        <v>-142000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>16770000</v>
       </c>
       <c r="E4" t="n">
-        <v>-817000</v>
+        <v>-13000</v>
       </c>
       <c r="F4" t="n">
+        <v>38936000</v>
+      </c>
+      <c r="G4" t="n">
         <v>12577000</v>
       </c>
-      <c r="G4" t="n">
-        <v>13932000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-23000</v>
+        <v>-47000</v>
       </c>
       <c r="I4" t="n">
-        <v>-1332000</v>
+        <v>26406000</v>
       </c>
       <c r="J4" t="n">
-        <v>-770000</v>
+        <v>16150000</v>
       </c>
       <c r="K4" t="n">
-        <v>-48000</v>
+        <v>-60000</v>
       </c>
       <c r="L4" t="n">
-        <v>-244000</v>
+        <v>16628000</v>
       </c>
       <c r="M4" t="n">
-        <v>-244000</v>
+        <v>16628000</v>
       </c>
       <c r="N4" t="n">
-        <v>-244000</v>
+        <v>-142000</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>16770000</v>
       </c>
       <c r="P4" t="n">
-        <v>-4426000</v>
+        <v>11754000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3847000</v>
+        <v>11107000</v>
       </c>
       <c r="R4" t="n">
-        <v>162000</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+        <v>659000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
       <c r="U4" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-736000</v>
+        <v>-12000</v>
       </c>
       <c r="X4" t="n">
-        <v>76000</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-812000</v>
+        <v>-13000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3864000</v>
+        <v>-1498000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-609000</v>
+        <v>-1262000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-546000</v>
+        <v>1132000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>308000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1601000</v>
+        <v>-1353000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1714000</v>
+        <v>921000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-433000</v>
+        <v>1256000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-109000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>24000</v>
-      </c>
+        <v>58000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>1964000</v>
+        <v>1889000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1949000</v>
+        <v>1877000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>313000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-74000</v>
+        <v>-1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3214000</v>
+        <v>-4127000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1579000</v>
+        <v>-3049000</v>
       </c>
       <c r="C5" t="n">
-        <v>-693000</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>-147000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="n">
-        <v>-499000</v>
+        <v>-281000</v>
       </c>
       <c r="F5" t="n">
-        <v>13932000</v>
+        <v>36225000</v>
       </c>
       <c r="G5" t="n">
-        <v>10602000</v>
+        <v>38936000</v>
       </c>
       <c r="H5" t="n">
-        <v>191000</v>
+        <v>59000</v>
       </c>
       <c r="I5" t="n">
-        <v>3139000</v>
+        <v>-2770000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1138000</v>
+        <v>-674000</v>
       </c>
       <c r="K5" t="n">
-        <v>-78000</v>
+        <v>-56000</v>
       </c>
       <c r="L5" t="n">
-        <v>-693000</v>
+        <v>-147000</v>
       </c>
       <c r="M5" t="n">
-        <v>-693000</v>
+        <v>-147000</v>
       </c>
       <c r="N5" t="n">
-        <v>-693000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>-147000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
-        <v>5357000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5828000</v>
-      </c>
+        <v>672000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>20000</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>-12000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-12000</v>
-      </c>
+        <v>958000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-479000</v>
+        <v>-281000</v>
       </c>
       <c r="X5" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-487000</v>
+        <v>-281000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1080000</v>
+        <v>-2768000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-191000</v>
+        <v>-514000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-545000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>-601000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>60000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>1649000</v>
+        <v>-616000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-577000</v>
+        <v>-37000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1617000</v>
+        <v>-8000</v>
       </c>
       <c r="AG5" t="n">
-        <v>61000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-142000</v>
-      </c>
+        <v>-93000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>2278000</v>
+        <v>1595000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21000</v>
+        <v>9000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2257000</v>
+        <v>1586000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-75000</v>
+        <v>-185000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-2540000</v>
+        <v>-2907000</v>
       </c>
     </row>
   </sheetData>
@@ -3451,187 +3451,187 @@
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="AD2" t="n">
         <v>30000</v>
@@ -3767,7 +3767,7 @@
         <v>30000</v>
       </c>
       <c r="AF2" t="n">
-        <v>5000</v>
+        <v>1864</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -3809,10 +3809,10 @@
         <v>8.852914999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.14002</v>
+        <v>0.14</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.258085</v>
+        <v>0.234585</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3850,10 +3850,10 @@
         <v>1000000000</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.17177641</v>
+        <v>0.16980337</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.81501293</v>
+        <v>0.8244831</v>
       </c>
       <c r="BI2" t="n">
         <v>1735603200</v>
@@ -3877,10 +3877,10 @@
         <v>-45.949</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.6626506</v>
+        <v>-0.6853932</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -3987,140 +3987,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CU2" t="n">
-        <v>-1.9997358e-05</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>-0.00014281788</v>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
       </c>
       <c r="CW2" t="n">
-        <v>-0.11808501</v>
+        <v>1864</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0.45754308</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>0.14 - 0.7</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-68.53932</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1756378740</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1756987200</v>
+      </c>
+      <c r="DF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.094585</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.4032014</v>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1531704600000</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.001000002</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>0.14 - 0.14</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>1774577335</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>finmb_572522100</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>FSM Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>FSM HOLDINGS</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
         <v>15</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="EA2" t="n">
         <v>15</v>
       </c>
-      <c r="DA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>finmb_572522100</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>FSM Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1774577335</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>FSM HOLDINGS</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1531704600000</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.001000002</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0.14 - 0.14</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>0.14 - 0.7</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-66.26506000000001</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1756378740</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1756987200</v>
-      </c>
       <c r="EB2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0.04</v>
+        <v>-0.7092213000000001</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0.7092213000000001</v>
-      </c>
-      <c r="EE2" t="n">
         <v>0.14</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
